--- a/artfynd/A 45167-2024 artfynd.xlsx
+++ b/artfynd/A 45167-2024 artfynd.xlsx
@@ -1130,7 +1130,7 @@
         <v>121735722</v>
       </c>
       <c r="B6" t="n">
-        <v>90748</v>
+        <v>90762</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 45167-2024 artfynd.xlsx
+++ b/artfynd/A 45167-2024 artfynd.xlsx
@@ -1130,7 +1130,7 @@
         <v>121735722</v>
       </c>
       <c r="B6" t="n">
-        <v>90762</v>
+        <v>90764</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 45167-2024 artfynd.xlsx
+++ b/artfynd/A 45167-2024 artfynd.xlsx
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124424540</v>
+        <v>124424423</v>
       </c>
       <c r="B7" t="n">
         <v>108639</v>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534767</v>
+        <v>534751</v>
       </c>
       <c r="R7" t="n">
         <v>6353649</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124424423</v>
+        <v>124424540</v>
       </c>
       <c r="B8" t="n">
         <v>108639</v>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534751</v>
+        <v>534767</v>
       </c>
       <c r="R8" t="n">
         <v>6353649</v>

--- a/artfynd/A 45167-2024 artfynd.xlsx
+++ b/artfynd/A 45167-2024 artfynd.xlsx
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124424423</v>
+        <v>124424540</v>
       </c>
       <c r="B7" t="n">
         <v>108639</v>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534751</v>
+        <v>534767</v>
       </c>
       <c r="R7" t="n">
         <v>6353649</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124424540</v>
+        <v>124424423</v>
       </c>
       <c r="B8" t="n">
         <v>108639</v>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534767</v>
+        <v>534751</v>
       </c>
       <c r="R8" t="n">
         <v>6353649</v>

--- a/artfynd/A 45167-2024 artfynd.xlsx
+++ b/artfynd/A 45167-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>88217911</v>
       </c>
       <c r="B2" t="n">
-        <v>92502</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Philonotis arnellii</t>
+          <t>Philonotis capillaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Husn.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534747.6011761016</v>
+        <v>534748</v>
       </c>
       <c r="R2" t="n">
-        <v>6353697.590048472</v>
+        <v>6353698</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,57 +782,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88764142</v>
+        <v>113006128</v>
       </c>
       <c r="B3" t="n">
-        <v>107257</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230629</v>
+        <v>3739</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Karelsk maskros</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Taraxacum isthmicola</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Virserum, 300 m SV vattentornet, Sm</t>
+          <t>Ekeflovägen 16 , Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534771.26886649</v>
+        <v>534755</v>
       </c>
       <c r="R3" t="n">
-        <v>6353649.73846265</v>
+        <v>6353642</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2008-05-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2008-05-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,35 +868,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Sandig mark på vägkant</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Nilsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Nilsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113006128</v>
+        <v>115065625</v>
       </c>
       <c r="B4" t="n">
-        <v>86236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,27 +894,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3739</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ekeflovägen 16 , Sm</t>
@@ -992,12 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +962,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115065625</v>
+        <v>121735722</v>
       </c>
       <c r="B5" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,17 +1011,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ekeflovägen 16 , Sm</t>
+          <t>Ekeflovägen 16 , Ekeflovägen 16 , Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534755</v>
+        <v>534768</v>
       </c>
       <c r="R5" t="n">
-        <v>6353642</v>
+        <v>6353662</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,12 +1045,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1077,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121735722</v>
+        <v>124424103</v>
       </c>
       <c r="B6" t="n">
-        <v>90781</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,37 +1088,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ekeflovägen 16 , Ekeflovägen 16 , Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534768</v>
+        <v>534731</v>
       </c>
       <c r="R6" t="n">
-        <v>6353662</v>
+        <v>6353629</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,15 +1179,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124424540</v>
+        <v>124424258</v>
       </c>
       <c r="B7" t="n">
-        <v>108639</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,13 +1214,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534767</v>
+        <v>534736</v>
       </c>
       <c r="R7" t="n">
-        <v>6353649</v>
+        <v>6353619</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,12 +1279,7 @@
         <v>124424423</v>
       </c>
       <c r="B8" t="n">
-        <v>108639</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,6 +1370,313 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124424540</v>
+      </c>
+      <c r="B9" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ekeflovägen 16 , Ekeflovägen 16 , Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>534767</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6353649</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100665942</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101346</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222886</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ekeflodsvägen, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>534702</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6353695</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>88764142</v>
+      </c>
+      <c r="B11" t="n">
+        <v>110401</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>230629</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Karelsk maskros</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Taraxacum isthmicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>H. Lindb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Virserum, 300 m SV vattentornet, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>534771</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6353650</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2008-05-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2008-05-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Sandig mark på vägkant</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tommy Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Nilsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45167-2024 artfynd.xlsx
+++ b/artfynd/A 45167-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88217911</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115065625</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121735722</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124424103</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124424258</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124424423</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124424540</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100665942</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,8 +1727,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88764142</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>